--- a/result.xlsx
+++ b/result.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Randomizer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\projects\github.com\Demparty\an.mn\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19C6652-6467-4D71-B505-2CB991F7CAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>total_pool</t>
   </si>
@@ -46,13 +47,19 @@
   </si>
   <si>
     <t>[6, 4, 33, 14, 20, 28, 11, 30]</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>uuriin_hayg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,6 +71,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -101,11 +116,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -407,77 +423,86 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C2">
         <v>15</v>
       </c>
-      <c r="B2">
+      <c r="D2">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C3">
         <v>20</v>
       </c>
-      <c r="B3">
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C4">
         <v>13</v>
       </c>
-      <c r="B4">
+      <c r="D4">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C5">
         <v>35</v>
       </c>
-      <c r="B5">
+      <c r="D5">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>5</v>
       </c>
     </row>

--- a/result.xlsx
+++ b/result.xlsx
@@ -1,95 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\projects\github.com\Demparty\an.mn\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19C6652-6467-4D71-B505-2CB991F7CAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
-  <si>
-    <t>total_pool</t>
-  </si>
-  <si>
-    <t>choose_pool</t>
-  </si>
-  <si>
-    <t>chosen</t>
-  </si>
-  <si>
-    <t>row_finished_on</t>
-  </si>
-  <si>
-    <t>[4, 14, 11]</t>
-  </si>
-  <si>
-    <t>2025-12-05</t>
-  </si>
-  <si>
-    <t>[13, 15]</t>
-  </si>
-  <si>
-    <t>[7, 13, 1, 4, 9, 2]</t>
-  </si>
-  <si>
-    <t>[6, 4, 33, 14, 20, 28, 11, 30]</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>uuriin_hayg</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -97,45 +42,85 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -423,87 +408,173 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>uuriin_hayg</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>total_pool</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>choose_pool</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>chosen</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>row_finished_on</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>first_5_blocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>test 1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[4, 14, 11]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>['00000000000000000000361658a877f3075a48da2b7d0c4583f742c8f5c38689', '000000000000000000013906e3a18a6ba9c3a27cb14d1f57a710bda5ac23dd14', '000000000000000000018090bab6a4752d60aa12efb21d7033d29b18fd128862', '00000000000000000000517189a681035b68daa77a0fb08a76ad67420fbaab98', '00000000000000000000f4072dc6b3dabc3d13502ebc13cc4b89812fef79e2fb']</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>test 2</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[13, 15]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>['00000000000000000000361658a877f3075a48da2b7d0c4583f742c8f5c38689', '000000000000000000013906e3a18a6ba9c3a27cb14d1f57a710bda5ac23dd14', '000000000000000000018090bab6a4752d60aa12efb21d7033d29b18fd128862', '00000000000000000000517189a681035b68daa77a0fb08a76ad67420fbaab98', '00000000000000000000f4072dc6b3dabc3d13502ebc13cc4b89812fef79e2fb']</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>test 3</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>[7, 13, 1, 4, 9, 2]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>['00000000000000000000361658a877f3075a48da2b7d0c4583f742c8f5c38689', '000000000000000000013906e3a18a6ba9c3a27cb14d1f57a710bda5ac23dd14', '000000000000000000018090bab6a4752d60aa12efb21d7033d29b18fd128862', '00000000000000000000517189a681035b68daa77a0fb08a76ad67420fbaab98', '00000000000000000000f4072dc6b3dabc3d13502ebc13cc4b89812fef79e2fb']</t>
+        </is>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="C2">
-        <v>15</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="F2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="C3">
-        <v>20</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="C4">
-        <v>13</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="C5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>test 4</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>35</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>8</v>
       </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>5</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>[6, 4, 33, 14, 20, 28, 11, 30]</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>['00000000000000000000361658a877f3075a48da2b7d0c4583f742c8f5c38689', '000000000000000000013906e3a18a6ba9c3a27cb14d1f57a710bda5ac23dd14', '000000000000000000018090bab6a4752d60aa12efb21d7033d29b18fd128862', '00000000000000000000517189a681035b68daa77a0fb08a76ad67420fbaab98', '00000000000000000000f4072dc6b3dabc3d13502ebc13cc4b89812fef79e2fb']</t>
+        </is>
       </c>
     </row>
   </sheetData>
